--- a/business_forms/043_expression_of_interest_form--business_forms.xlsx
+++ b/business_forms/043_expression_of_interest_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>Full Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>educational_history</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>Educational Background</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,41 +589,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>job_title_and_category</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>educational_history</t>
+          <t>Job Title and Category</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>job_status</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>Job Status</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,58 +635,58 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>Job Level</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>job_category</t>
+          <t>job_type</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>job_category</t>
+          <t>Job Type</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>job_status</t>
+          <t>job_location</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>job_status</t>
+          <t>Job Location</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,41 +704,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>job_level</t>
+          <t>job_start_and_end_dates</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>job_level</t>
+          <t>Job Start and End Dates</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>job_type</t>
+          <t>job_status_update</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>job_type</t>
+          <t>Job Status Update</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,340 +750,64 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>job_location</t>
+          <t>job_status_reason</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>job_location</t>
+          <t>Job Status Reason</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>job_start_date</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>job_start_date</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>job_end_date</t>
+          <t>cover_letter</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>job_end_date</t>
+          <t>Cover Letter</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>job_status_update</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>job_status_update</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>job_status_updated_date</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>job_status_updated_date</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>job_status_reason</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>job_status_reason</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>job_category</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>job_category</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>job_level</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>job_level</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>job_type</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>job_type</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>job_location</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>job_location</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>resume</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>resume</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>cover_letter</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>cover_letter</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>job_start_date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>job_start_date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>job_end_date</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>job_end_date</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>job_status</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>job_status</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1131,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option_e</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option e</t>
         </is>
       </c>
     </row>
@@ -1148,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option_f</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option f</t>
         </is>
       </c>
     </row>
@@ -1165,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option_g</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option g</t>
         </is>
       </c>
     </row>
@@ -1182,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_d</t>
+          <t>option_h</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_d</t>
+          <t>option h</t>
         </is>
       </c>
     </row>
@@ -1199,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_e</t>
+          <t>option_i</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_e</t>
+          <t>option i</t>
         </is>
       </c>
     </row>
@@ -1216,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_f</t>
+          <t>option_j</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_f</t>
+          <t>option j</t>
         </is>
       </c>
     </row>
@@ -1233,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_g</t>
+          <t>option_k</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_g</t>
+          <t>option k</t>
         </is>
       </c>
     </row>
@@ -1250,216 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_h</t>
+          <t>option_l</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_h</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>job_category_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option_i</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>option_i</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>job_category_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>option_j</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>option_j</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>job_category_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>option_k</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>option_k</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>job_category_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option_l</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>option_l</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>job_type_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option_m</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>option_m</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>job_type_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option_n</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>option_n</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>job_type_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option_o</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>option_o</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>job_type_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option_p</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>option_p</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>job_status_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option_q</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>option_q</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>job_status_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option_r</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>option_r</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>job_status_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option_s</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>option_s</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>job_status_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option_t</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>option_t</t>
+          <t>option l</t>
         </is>
       </c>
     </row>
